--- a/mygui_docking/Project1/Project1/data/JY61P_sync.xlsx
+++ b/mygui_docking/Project1/Project1/data/JY61P_sync.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10812"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28925"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/Troldal/Development/bin2c/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mxnkilmt\Documents\GitHub\ZJU_Oil\mygui_docking\Project1\Project1\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{AC33A6FB-1603-2641-A40F-B7C7F2B0E698}" xr6:coauthVersionLast="44" xr6:coauthVersionMax="44" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{97894B66-8E76-4ABC-911B-F8A35596D95D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2780" yWindow="1560" windowWidth="28040" windowHeight="17440" xr2:uid="{FF49B81A-127A-B44C-A44B-FF0F3EF8FCF9}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{FF49B81A-127A-B44C-A44B-FF0F3EF8FCF9}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,10 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <si>
-    <t/>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="26">
   <si>
     <t>Time</t>
   </si>
@@ -95,39 +92,44 @@
     <t>Device 0x0D Angle Z</t>
   </si>
   <si>
-    <t>2025-07-10 13:18:04</t>
-  </si>
-  <si>
-    <t>2025-07-10 13:18:05</t>
-  </si>
-  <si>
-    <t>2025-07-10 13:18:06</t>
-  </si>
-  <si>
-    <t>2025-07-10 13:18:07</t>
-  </si>
-  <si>
-    <t>2025-07-10 13:18:08</t>
-  </si>
-  <si>
-    <t>2025-07-10 13:18:09</t>
-  </si>
-  <si>
-    <t>2025-07-10 13:18:10</t>
+    <t>2025-07-14 11:17:31</t>
+  </si>
+  <si>
+    <t>2025-07-14 11:17:32</t>
+  </si>
+  <si>
+    <t>2025-07-14 11:17:33</t>
+  </si>
+  <si>
+    <t>2025-07-14 11:17:34</t>
+  </si>
+  <si>
+    <t>2025-07-14 11:17:35</t>
+  </si>
+  <si>
+    <t>2025-07-14 11:17:36</t>
+  </si>
+  <si>
+    <t>2025-07-14 11:17:37</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts>
-	</numFmts>
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="等线"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="等线"/>
+      <family val="3"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -155,7 +157,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -171,7 +173,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 主题​​">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -467,104 +469,486 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{049FB1B4-2A61-4643-8816-8B76EC36FD4B}">
-  <dimension ref="A1"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:S8"/>
+  <sheetFormatPr defaultColWidth="10.90625" defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="19.6328125" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
         <v>1</v>
       </c>
-      <c r="B1" t="s">
+      <c r="C1" t="s">
         <v>2</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
         <v>3</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>4</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>5</v>
       </c>
-      <c r="F1" t="s">
+      <c r="G1" t="s">
         <v>6</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
         <v>7</v>
       </c>
-      <c r="H1" t="s">
+      <c r="I1" t="s">
         <v>8</v>
       </c>
-      <c r="I1" t="s">
+      <c r="J1" t="s">
         <v>9</v>
       </c>
-      <c r="J1" t="s">
+      <c r="K1" t="s">
         <v>10</v>
       </c>
-      <c r="K1" t="s">
+      <c r="L1" t="s">
         <v>11</v>
       </c>
-      <c r="L1" t="s">
+      <c r="M1" t="s">
         <v>12</v>
       </c>
-      <c r="M1" t="s">
+      <c r="N1" t="s">
         <v>13</v>
       </c>
-      <c r="N1" t="s">
+      <c r="O1" t="s">
         <v>14</v>
       </c>
-      <c r="O1" t="s">
+      <c r="P1" t="s">
         <v>15</v>
       </c>
-      <c r="P1" t="s">
+      <c r="Q1" t="s">
         <v>16</v>
       </c>
-      <c r="Q1" t="s">
+      <c r="R1" t="s">
         <v>17</v>
       </c>
-      <c r="R1" t="s">
+      <c r="S1" t="s">
         <v>18</v>
       </c>
-      <c r="S1" t="s">
+    </row>
+    <row r="2" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
         <v>19</v>
       </c>
+      <c r="B2">
+        <v>-5.37109375E-3</v>
+      </c>
+      <c r="C2">
+        <v>-0.50830078125</v>
+      </c>
+      <c r="D2">
+        <v>0.84619140625</v>
+      </c>
+      <c r="E2">
+        <v>6.103515625E-2</v>
+      </c>
+      <c r="F2">
+        <v>0</v>
+      </c>
+      <c r="G2">
+        <v>0</v>
+      </c>
+      <c r="H2">
+        <v>-31.04736328125</v>
+      </c>
+      <c r="I2">
+        <v>0.32958984375</v>
+      </c>
+      <c r="J2">
+        <v>3.4552001953125</v>
+      </c>
+      <c r="K2">
+        <v>-5.37109375E-3</v>
+      </c>
+      <c r="L2">
+        <v>-0.50830078125</v>
+      </c>
+      <c r="M2">
+        <v>0.84619140625</v>
+      </c>
+      <c r="N2">
+        <v>6.103515625E-2</v>
+      </c>
+      <c r="O2">
+        <v>0</v>
+      </c>
+      <c r="P2">
+        <v>0</v>
+      </c>
+      <c r="Q2">
+        <v>-31.04736328125</v>
+      </c>
+      <c r="R2">
+        <v>0.32958984375</v>
+      </c>
+      <c r="S2">
+        <v>3.4552001953125</v>
+      </c>
     </row>
-    <row r="2">
-      <c r="A2" t="s">
+    <row r="3" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
         <v>20</v>
       </c>
+      <c r="B3">
+        <v>-5.37109375E-3</v>
+      </c>
+      <c r="C3">
+        <v>-0.5107421875</v>
+      </c>
+      <c r="D3">
+        <v>0.8427734375</v>
+      </c>
+      <c r="E3">
+        <v>-0.1220703125</v>
+      </c>
+      <c r="F3">
+        <v>0</v>
+      </c>
+      <c r="G3">
+        <v>0</v>
+      </c>
+      <c r="H3">
+        <v>-31.058349609375</v>
+      </c>
+      <c r="I3">
+        <v>0.32958984375</v>
+      </c>
+      <c r="J3">
+        <v>3.4552001953125</v>
+      </c>
+      <c r="K3">
+        <v>-5.37109375E-3</v>
+      </c>
+      <c r="L3">
+        <v>-0.5107421875</v>
+      </c>
+      <c r="M3">
+        <v>0.8427734375</v>
+      </c>
+      <c r="N3">
+        <v>-0.1220703125</v>
+      </c>
+      <c r="O3">
+        <v>0</v>
+      </c>
+      <c r="P3">
+        <v>0</v>
+      </c>
+      <c r="Q3">
+        <v>-31.058349609375</v>
+      </c>
+      <c r="R3">
+        <v>0.32958984375</v>
+      </c>
+      <c r="S3">
+        <v>3.4552001953125</v>
+      </c>
     </row>
-    <row r="3">
-      <c r="A3" t="s">
+    <row r="4" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
         <v>21</v>
       </c>
+      <c r="B4">
+        <v>-5.859375E-3</v>
+      </c>
+      <c r="C4">
+        <v>-0.50927734375</v>
+      </c>
+      <c r="D4">
+        <v>0.845703125</v>
+      </c>
+      <c r="E4">
+        <v>0</v>
+      </c>
+      <c r="F4">
+        <v>0</v>
+      </c>
+      <c r="G4">
+        <v>0</v>
+      </c>
+      <c r="H4">
+        <v>-31.058349609375</v>
+      </c>
+      <c r="I4">
+        <v>0.32958984375</v>
+      </c>
+      <c r="J4">
+        <v>3.4552001953125</v>
+      </c>
+      <c r="K4">
+        <v>-5.37109375E-3</v>
+      </c>
+      <c r="L4">
+        <v>-0.509765625</v>
+      </c>
+      <c r="M4">
+        <v>0.84326171875</v>
+      </c>
+      <c r="N4">
+        <v>0</v>
+      </c>
+      <c r="O4">
+        <v>0</v>
+      </c>
+      <c r="P4">
+        <v>0</v>
+      </c>
+      <c r="Q4">
+        <v>-31.0638427734375</v>
+      </c>
+      <c r="R4">
+        <v>0.32958984375</v>
+      </c>
+      <c r="S4">
+        <v>3.4552001953125</v>
+      </c>
     </row>
-    <row r="4">
-      <c r="A4" t="s">
+    <row r="5" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
         <v>22</v>
       </c>
+      <c r="B5">
+        <v>-5.37109375E-3</v>
+      </c>
+      <c r="C5">
+        <v>-0.50927734375</v>
+      </c>
+      <c r="D5">
+        <v>0.84521484375</v>
+      </c>
+      <c r="E5">
+        <v>-0.244140625</v>
+      </c>
+      <c r="F5">
+        <v>0</v>
+      </c>
+      <c r="G5">
+        <v>0</v>
+      </c>
+      <c r="H5">
+        <v>-31.0638427734375</v>
+      </c>
+      <c r="I5">
+        <v>0.32958984375</v>
+      </c>
+      <c r="J5">
+        <v>3.4552001953125</v>
+      </c>
+      <c r="K5">
+        <v>-5.37109375E-3</v>
+      </c>
+      <c r="L5">
+        <v>-0.5087890625</v>
+      </c>
+      <c r="M5">
+        <v>0.84375</v>
+      </c>
+      <c r="N5">
+        <v>-6.103515625E-2</v>
+      </c>
+      <c r="O5">
+        <v>0</v>
+      </c>
+      <c r="P5">
+        <v>0</v>
+      </c>
+      <c r="Q5">
+        <v>-31.0638427734375</v>
+      </c>
+      <c r="R5">
+        <v>0.32958984375</v>
+      </c>
+      <c r="S5">
+        <v>3.4552001953125</v>
+      </c>
     </row>
-    <row r="5">
-      <c r="A5" t="s">
+    <row r="6" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
         <v>23</v>
       </c>
+      <c r="B6">
+        <v>-5.37109375E-3</v>
+      </c>
+      <c r="C6">
+        <v>-0.50927734375</v>
+      </c>
+      <c r="D6">
+        <v>0.84375</v>
+      </c>
+      <c r="E6">
+        <v>-6.103515625E-2</v>
+      </c>
+      <c r="F6">
+        <v>0</v>
+      </c>
+      <c r="G6">
+        <v>0</v>
+      </c>
+      <c r="H6">
+        <v>-31.0638427734375</v>
+      </c>
+      <c r="I6">
+        <v>0.32958984375</v>
+      </c>
+      <c r="J6">
+        <v>3.4552001953125</v>
+      </c>
+      <c r="K6">
+        <v>-5.37109375E-3</v>
+      </c>
+      <c r="L6">
+        <v>-0.509765625</v>
+      </c>
+      <c r="M6">
+        <v>0.84423828125</v>
+      </c>
+      <c r="N6">
+        <v>0.18310546875</v>
+      </c>
+      <c r="O6">
+        <v>0</v>
+      </c>
+      <c r="P6">
+        <v>0</v>
+      </c>
+      <c r="Q6">
+        <v>-31.0638427734375</v>
+      </c>
+      <c r="R6">
+        <v>0.32958984375</v>
+      </c>
+      <c r="S6">
+        <v>3.4552001953125</v>
+      </c>
     </row>
-    <row r="6">
-      <c r="A6" t="s">
+    <row r="7" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
         <v>24</v>
       </c>
+      <c r="B7">
+        <v>-5.37109375E-3</v>
+      </c>
+      <c r="C7">
+        <v>-0.50927734375</v>
+      </c>
+      <c r="D7">
+        <v>0.84423828125</v>
+      </c>
+      <c r="E7">
+        <v>0.18310546875</v>
+      </c>
+      <c r="F7">
+        <v>0</v>
+      </c>
+      <c r="G7">
+        <v>0</v>
+      </c>
+      <c r="H7">
+        <v>-31.058349609375</v>
+      </c>
+      <c r="I7">
+        <v>0.32958984375</v>
+      </c>
+      <c r="J7">
+        <v>3.4552001953125</v>
+      </c>
+      <c r="K7">
+        <v>-4.8828125E-3</v>
+      </c>
+      <c r="L7">
+        <v>-0.5087890625</v>
+      </c>
+      <c r="M7">
+        <v>0.845703125</v>
+      </c>
+      <c r="N7">
+        <v>6.103515625E-2</v>
+      </c>
+      <c r="O7">
+        <v>0</v>
+      </c>
+      <c r="P7">
+        <v>0</v>
+      </c>
+      <c r="Q7">
+        <v>-31.058349609375</v>
+      </c>
+      <c r="R7">
+        <v>0.32958984375</v>
+      </c>
+      <c r="S7">
+        <v>3.4552001953125</v>
+      </c>
     </row>
-    <row r="7">
-      <c r="A7" t="s">
+    <row r="8" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="s">
-        <v>26</v>
+      <c r="B8">
+        <v>-5.37109375E-3</v>
+      </c>
+      <c r="C8">
+        <v>-0.50927734375</v>
+      </c>
+      <c r="D8">
+        <v>0.845703125</v>
+      </c>
+      <c r="E8">
+        <v>0</v>
+      </c>
+      <c r="F8">
+        <v>0</v>
+      </c>
+      <c r="G8">
+        <v>0</v>
+      </c>
+      <c r="H8">
+        <v>-31.058349609375</v>
+      </c>
+      <c r="I8">
+        <v>0.32958984375</v>
+      </c>
+      <c r="J8">
+        <v>3.4552001953125</v>
+      </c>
+      <c r="K8">
+        <v>-5.859375E-3</v>
+      </c>
+      <c r="L8">
+        <v>-0.51025390625</v>
+      </c>
+      <c r="M8">
+        <v>0.84423828125</v>
+      </c>
+      <c r="N8">
+        <v>0</v>
+      </c>
+      <c r="O8">
+        <v>0</v>
+      </c>
+      <c r="P8">
+        <v>0</v>
+      </c>
+      <c r="Q8">
+        <v>-31.058349609375</v>
+      </c>
+      <c r="R8">
+        <v>0.32958984375</v>
+      </c>
+      <c r="S8">
+        <v>3.4552001953125</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>